--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_356_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_356_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7614</v>
+        <v>5.9129</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2398</v>
+        <v>5.3577</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5216</v>
+        <v>0.5552</v>
       </c>
       <c r="G2" t="n">
         <v>2.6306</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0432</v>
+        <v>2.1947</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2151</v>
+        <v>1.333</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8617</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8141</v>
+        <v>3.9057</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8294</v>
+        <v>5.1238</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0153</v>
+        <v>-1.2181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3584</v>
+        <v>3.8019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.469</v>
+        <v>0.9712</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1105</v>
+        <v>2.8307</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3097</v>
+        <v>5.3213</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8913</v>
+        <v>1.7512</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4184</v>
+        <v>3.5701</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9513</v>
+        <v>-1.5194</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4223</v>
+        <v>-0.78</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.529</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2391</v>
+        <v>-0.288</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6948</v>
+        <v>0.1968</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5443</v>
+        <v>-0.4848</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1444</v>
+        <v>-0.5361</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>-0.3943</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.536</v>
+        <v>3.3924</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1238</v>
+        <v>3.2397</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5878</v>
+        <v>0.1527</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8019</v>
+        <v>0.3584</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9712</v>
+        <v>0.469</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8307</v>
+        <v>-0.1105</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3213</v>
+        <v>2.3097</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7512</v>
+        <v>0.8913</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5701</v>
+        <v>1.4184</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5194</v>
+        <v>-1.9513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.78</v>
+        <v>-0.4223</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.529</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6576</v>
+        <v>1.8174</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1968</v>
+        <v>1.1051</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8544</v>
+        <v>0.7123</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3943</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0635</v>
+        <v>2.8055</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0611</v>
+        <v>3.0047</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0025</v>
+        <v>-0.1992</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5385</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0659</v>
+        <v>0.8079</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.507</v>
+        <v>0.4367</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5729</v>
+        <v>0.3712</v>
       </c>
       <c r="V5" t="n">
         <v>2.1444</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6247</v>
+        <v>2.0794</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2595</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3652</v>
+        <v>1.466</v>
       </c>
       <c r="G6" t="n">
         <v>1.1091</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.322</v>
+        <v>0.1327</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0218</v>
+        <v>-0.2735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8127</v>
+        <v>0.9307</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8345</v>
+        <v>-1.2042</v>
       </c>
       <c r="G7" t="n">
         <v>0.2355</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0469</v>
+        <v>0.7951</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4288</v>
+        <v>0.5467</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6181</v>
+        <v>0.2484</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8359</v>
+        <v>-1.3908</v>
       </c>
       <c r="E8" t="n">
-        <v>1.894</v>
+        <v>1.7761</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7299</v>
+        <v>-3.1668</v>
       </c>
       <c r="G8" t="n">
         <v>0.8529</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1514</v>
+        <v>0.5966</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.4602</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5733</v>
+        <v>0.1364</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1444</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2563</v>
+        <v>-1.5228</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9663</v>
+        <v>0.8863</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2899</v>
+        <v>-2.4091</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6983</v>
+        <v>-0.6142</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3098</v>
+        <v>-0.2495</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3885</v>
+        <v>-0.3647</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3032</v>
+        <v>1.3658</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4271</v>
+        <v>0.1512</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1239</v>
+        <v>1.2146</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0016</v>
+        <v>-1.98</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7369</v>
+        <v>-0.4008</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2647</v>
+        <v>-1.5792</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7436</v>
+        <v>-0.8364</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0499</v>
+        <v>-0.4795</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6937</v>
+        <v>-0.3569</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6744</v>
+        <v>-1.8961</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7684</v>
+        <v>-1.4381</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4427</v>
+        <v>-0.458</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6142</v>
+        <v>-1.6983</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2495</v>
+        <v>-0.3098</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3647</v>
+        <v>-1.3885</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3658</v>
+        <v>0.3032</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1512</v>
+        <v>0.4271</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2146</v>
+        <v>-0.1239</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.98</v>
+        <v>-2.0016</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4008</v>
+        <v>-0.7369</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5792</v>
+        <v>-1.2647</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.988</v>
+        <v>1.1037</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3905</v>
+        <v>0.5256</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1533</v>
+        <v>-3.036</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4737</v>
+        <v>-0.5916</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6796</v>
+        <v>-2.4444</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1148</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1261</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.315</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7372</v>
+        <v>-4.8558</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9502</v>
+        <v>-3.3041</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.787</v>
+        <v>-1.5517</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1266</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8017</v>
+        <v>0.6831</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9006</v>
+        <v>0.5467</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0988</v>
+        <v>0.1364</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3247</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.120800000000001</v>
+        <v>5.120900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>15.5985</v>
+        <v>15.5986</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.4774</v>
+        <v>-10.4776</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1040000000000001</v>
@@ -1447,13 +1447,13 @@
         <v>10.2669</v>
       </c>
       <c r="L13" t="n">
-        <v>6.607200000000001</v>
+        <v>6.607199999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-16.9782</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.1177</v>
+        <v>-5.117700000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-11.8606</v>
@@ -1468,13 +1468,13 @@
         <v>11.5977</v>
       </c>
       <c r="S13" t="n">
-        <v>6.9981</v>
+        <v>6.997999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.700400000000001</v>
+        <v>4.7005</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2978</v>
+        <v>2.2975</v>
       </c>
       <c r="V13" t="n">
         <v>-2.933</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4602</v>
+        <v>4.1292</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3097</v>
+        <v>3.9559</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1504</v>
+        <v>0.1733</v>
       </c>
       <c r="G14" t="n">
         <v>1.5475</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.876</v>
+        <v>-1.207</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1766</v>
+        <v>-0.5305</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6994</v>
+        <v>-0.6765</v>
       </c>
       <c r="V14" t="n">
         <v>2.3969</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5981</v>
+        <v>2.0357</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4533</v>
+        <v>2.7034</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8552</v>
+        <v>-0.6677</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0032</v>
+        <v>2.253</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6503</v>
+        <v>1.6206</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6535</v>
+        <v>0.6325</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3337</v>
+        <v>3.7944</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9915</v>
+        <v>2.9478</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3422</v>
+        <v>0.8465</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3305</v>
+        <v>-1.5413</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6418</v>
+        <v>-1.3273</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3113</v>
+        <v>-0.214</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1163</v>
+        <v>-0.7018</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8804</v>
+        <v>-0.6091</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2359</v>
+        <v>-0.0927</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1444</v>
+        <v>0.2525</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4346</v>
+        <v>2.0313</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3495</v>
+        <v>3.8072</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.915</v>
+        <v>-1.7759</v>
       </c>
       <c r="G16" t="n">
-        <v>2.253</v>
+        <v>3.0032</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6206</v>
+        <v>-0.6503</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6325</v>
+        <v>3.6535</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7944</v>
+        <v>4.3337</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9478</v>
+        <v>0.9915</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8465</v>
+        <v>3.3422</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5413</v>
+        <v>-1.3305</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3273</v>
+        <v>-1.6418</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.214</v>
+        <v>0.3113</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.303</v>
+        <v>-0.6831</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.963</v>
+        <v>-0.5265</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.34</v>
+        <v>-0.1566</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2525</v>
+        <v>-2.1444</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4254</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.271</v>
+        <v>1.7314</v>
       </c>
       <c r="E17" t="n">
-        <v>2.759</v>
+        <v>2.9949</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.488</v>
+        <v>-1.2635</v>
       </c>
       <c r="G17" t="n">
         <v>1.7109</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5121</v>
+        <v>-1.0517</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8883</v>
+        <v>-0.6524</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6238</v>
+        <v>-0.3993</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4535</v>
+        <v>-0.2741</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3133</v>
+        <v>-0.5492</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1402</v>
+        <v>0.2751</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2736</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1593</v>
+        <v>-0.9799</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2434</v>
+        <v>-0.4793</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9159</v>
+        <v>-0.5006</v>
       </c>
       <c r="V18" t="n">
         <v>0.2836</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6438</v>
+        <v>-0.6145</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9388</v>
+        <v>0.5013</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5826</v>
+        <v>-1.1157</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6144</v>
+        <v>-1.159</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1862</v>
+        <v>-0.4128</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4282</v>
+        <v>-0.7461</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6698</v>
+        <v>0.5995</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0441</v>
+        <v>0.1344</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6257</v>
+        <v>0.465</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2842</v>
+        <v>-1.7584</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2303</v>
+        <v>-0.5473</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0539</v>
+        <v>-1.2112</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3623</v>
+        <v>0.0806</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3566</v>
+        <v>-0.0982</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0057</v>
+        <v>0.1788</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9341</v>
+        <v>-0.9957</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3833</v>
+        <v>0.7785</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3174</v>
+        <v>-1.7743</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.159</v>
+        <v>-1.0744</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4128</v>
+        <v>-0.4119</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7461</v>
+        <v>-0.6625</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5995</v>
+        <v>0.6841</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1344</v>
+        <v>0.2927</v>
       </c>
       <c r="L20" t="n">
-        <v>0.465</v>
+        <v>0.3914</v>
       </c>
       <c r="M20" t="n">
         <v>-1.7584</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5473</v>
+        <v>-0.7045</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2112</v>
+        <v>-1.0539</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.239</v>
+        <v>-0.1533</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>0.0944</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0228</v>
+        <v>-0.2478</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3661</v>
+        <v>-1.2707</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5426</v>
+        <v>-0.4889</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9087</v>
+        <v>-0.7817</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0744</v>
+        <v>-1.5439</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4119</v>
+        <v>0.1525</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6625</v>
+        <v>-1.6964</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6841</v>
+        <v>-0.7327</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2927</v>
+        <v>0.0168</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3914</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7584</v>
+        <v>-0.8112</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7045</v>
+        <v>0.1357</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0539</v>
+        <v>-0.9469</v>
       </c>
       <c r="P21" t="n">
         <v>0.232</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5236</v>
+        <v>0.0413</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1415</v>
+        <v>0.2438</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3822</v>
+        <v>-0.2025</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5738</v>
+        <v>-1.7555</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7248</v>
+        <v>0.9951</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.849</v>
+        <v>-2.7506</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5439</v>
+        <v>-1.6144</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1525</v>
+        <v>-1.1862</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6964</v>
+        <v>-0.4282</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7327</v>
+        <v>0.6698</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0168</v>
+        <v>0.0441</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.6257</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8112</v>
+        <v>-2.2842</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1357</v>
+        <v>-1.2303</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9469</v>
+        <v>-1.0539</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2618</v>
+        <v>0.2506</v>
       </c>
       <c r="T22" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.4129</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2697</v>
+        <v>-0.1623</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3509</v>
+        <v>-3.8569</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0269</v>
+        <v>-0.791</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.324</v>
+        <v>-3.0659</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8538</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2498</v>
+        <v>-0.7558</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4323</v>
+        <v>-0.1964</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8175</v>
+        <v>-0.5594</v>
       </c>
       <c r="V23" t="n">
         <v>0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5626</v>
+        <v>-4.7085</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1937</v>
+        <v>-3.4296</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3689</v>
+        <v>-1.2788</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8917</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1195</v>
+        <v>-0.2653</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2794</v>
+        <v>0.0435</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3989</v>
+        <v>-0.3088</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1209</v>
+        <v>-3.548300000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>10.4775</v>
+        <v>10.4776</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.5986</v>
+        <v>-14.0257</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1037999999999994</v>
+        <v>0.1038000000000012</v>
       </c>
       <c r="H25" t="n">
         <v>-5.1493</v>
       </c>
       <c r="I25" t="n">
-        <v>5.253400000000002</v>
+        <v>5.253399999999999</v>
       </c>
       <c r="J25" t="n">
         <v>16.9783</v>
       </c>
       <c r="K25" t="n">
-        <v>5.117599999999999</v>
+        <v>5.1176</v>
       </c>
       <c r="L25" t="n">
         <v>11.8605</v>
@@ -2404,13 +2404,13 @@
         <v>10.438</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.998100000000001</v>
+        <v>-5.425399999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.2977</v>
+        <v>-2.297800000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.7004</v>
+        <v>-3.1277</v>
       </c>
       <c r="V25" t="n">
         <v>2.933</v>
